--- a/output_excel/hosp2_resultados.xlsx
+++ b/output_excel/hosp2_resultados.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flopes\Documents\GitHub\Doutorado-real-datasets\output_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="SVM" sheetId="1" r:id="rId1"/>
-    <sheet name="GB" sheetId="2" r:id="rId2"/>
-    <sheet name="RF" sheetId="3" r:id="rId3"/>
+    <sheet name="(a) Gradient Boosting" sheetId="2" r:id="rId1"/>
+    <sheet name="(b) Random Forest" sheetId="3" r:id="rId2"/>
+    <sheet name="(c) Support Vector Machine" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -72,8 +77,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,13 +141,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Escritório">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -180,9 +193,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Escritório">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -214,9 +227,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -248,9 +262,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Escritório">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -423,11 +438,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,145 +486,145 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.8496275293051004</v>
+        <v>0.83465834851041476</v>
       </c>
       <c r="C2">
-        <v>0.01325641427377439</v>
+        <v>1.312867133409275E-2</v>
       </c>
       <c r="D2">
-        <v>0.8450352168726756</v>
+        <v>0.83232998258960333</v>
       </c>
       <c r="E2">
-        <v>0.01420956441738021</v>
+        <v>1.1640109442124749E-2</v>
       </c>
       <c r="F2">
-        <v>0.846983477621799</v>
+        <v>0.81682943506686601</v>
       </c>
       <c r="G2">
-        <v>0.01652818978398794</v>
+        <v>2.9380517144572911E-2</v>
       </c>
       <c r="H2">
-        <v>0.8494598011409538</v>
+        <v>0.83717157058918124</v>
       </c>
       <c r="I2">
-        <v>0.01544317459164301</v>
+        <v>9.6047505223339526E-3</v>
       </c>
       <c r="J2">
-        <v>0.8476922847834064</v>
+        <v>0.84012814134624736</v>
       </c>
       <c r="K2">
-        <v>0.0153751521932838</v>
+        <v>1.6783801370710439E-2</v>
       </c>
       <c r="L2">
-        <v>0.8477868837898146</v>
+        <v>0.83739864288090438</v>
       </c>
       <c r="M2">
-        <v>0.01516005070158696</v>
+        <v>1.7299864732806331E-2</v>
       </c>
       <c r="N2">
-        <v>0.8503131629427656</v>
+        <v>0.84196254262101111</v>
       </c>
       <c r="O2">
-        <v>0.01817722190142798</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>1.47966186807174E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.7791950665368388</v>
+        <v>0.78915936384290819</v>
       </c>
       <c r="C3">
-        <v>0.01424211290595091</v>
+        <v>4.5775640211467489E-2</v>
       </c>
       <c r="D3">
-        <v>0.7843232716650438</v>
+        <v>0.77659850697825383</v>
       </c>
       <c r="E3">
-        <v>0.02304732303514044</v>
+        <v>3.9993550219367291E-2</v>
       </c>
       <c r="F3">
-        <v>0.7868873742291465</v>
+        <v>0.75611814345991557</v>
       </c>
       <c r="G3">
-        <v>0.03216077092338546</v>
+        <v>5.7110293048738027E-2</v>
       </c>
       <c r="H3">
-        <v>0.7791950665368387</v>
+        <v>0.77140538786108392</v>
       </c>
       <c r="I3">
-        <v>0.02763413365597731</v>
+        <v>3.745331840421523E-2</v>
       </c>
       <c r="J3">
-        <v>0.7842259006815969</v>
+        <v>0.77663096397273612</v>
       </c>
       <c r="K3">
-        <v>0.02410398979048227</v>
+        <v>1.171693005374198E-2</v>
       </c>
       <c r="L3">
-        <v>0.7842259006815969</v>
+        <v>0.76900357026939292</v>
       </c>
       <c r="M3">
-        <v>0.02410398979048227</v>
+        <v>1.7026625002992238E-2</v>
       </c>
       <c r="N3">
-        <v>0.7944823109380071</v>
+        <v>0.78429081467056139</v>
       </c>
       <c r="O3">
-        <v>0.023711828235777</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2.3360694894243871E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.7730484108847506</v>
+        <v>0.74426800213934952</v>
       </c>
       <c r="C4">
-        <v>0.02361669050261545</v>
+        <v>9.8728467877289266E-3</v>
       </c>
       <c r="D4">
-        <v>0.7735647720458341</v>
+        <v>0.76082397367951915</v>
       </c>
       <c r="E4">
-        <v>0.0219440250663419</v>
+        <v>4.7928815133450016E-3</v>
       </c>
       <c r="F4">
-        <v>0.7659117356282719</v>
+        <v>0.71829241017163414</v>
       </c>
       <c r="G4">
-        <v>0.02831726159006452</v>
+        <v>6.1974389834021391E-2</v>
       </c>
       <c r="H4">
-        <v>0.7674436394872044</v>
+        <v>0.75980162396071382</v>
       </c>
       <c r="I4">
-        <v>0.02000738032754627</v>
+        <v>1.6678941138236879E-2</v>
       </c>
       <c r="J4">
-        <v>0.7755958574415326</v>
+        <v>0.75853130419280068</v>
       </c>
       <c r="K4">
-        <v>0.01923885209558635</v>
+        <v>1.9123239507910759E-2</v>
       </c>
       <c r="L4">
-        <v>0.7748318503751965</v>
+        <v>0.76922837555307055</v>
       </c>
       <c r="M4">
-        <v>0.01874594018389669</v>
+        <v>1.5783164346214341E-2</v>
       </c>
       <c r="N4">
-        <v>0.7702445665386299</v>
+        <v>0.76209137615273659</v>
       </c>
       <c r="O4">
-        <v>0.02410052465690725</v>
+        <v>2.4173206686636979E-2</v>
       </c>
     </row>
   </sheetData>
@@ -618,11 +633,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -666,145 +681,145 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.8346583485104148</v>
+        <v>0.84373870967947262</v>
       </c>
       <c r="C2">
-        <v>0.01312867133409275</v>
+        <v>1.256900327228387E-2</v>
       </c>
       <c r="D2">
-        <v>0.8323299825896033</v>
+        <v>0.84307855137112786</v>
       </c>
       <c r="E2">
-        <v>0.01164010944212475</v>
+        <v>7.775781461952529E-3</v>
       </c>
       <c r="F2">
-        <v>0.816829435066866</v>
+        <v>0.81999860705464445</v>
       </c>
       <c r="G2">
-        <v>0.02938051714457291</v>
+        <v>2.270744622635501E-2</v>
       </c>
       <c r="H2">
-        <v>0.8371715705891812</v>
+        <v>0.84153052858841215</v>
       </c>
       <c r="I2">
-        <v>0.009604750522333953</v>
+        <v>1.115519043987993E-2</v>
       </c>
       <c r="J2">
-        <v>0.8401281413462474</v>
+        <v>0.8489145338124624</v>
       </c>
       <c r="K2">
-        <v>0.01678380137071044</v>
+        <v>1.1118633806529041E-2</v>
       </c>
       <c r="L2">
-        <v>0.8373986428809044</v>
+        <v>0.84659220411093405</v>
       </c>
       <c r="M2">
-        <v>0.01729986473280633</v>
+        <v>1.023912918420117E-2</v>
       </c>
       <c r="N2">
-        <v>0.8419625426210111</v>
+        <v>0.84394849571922603</v>
       </c>
       <c r="O2">
-        <v>0.0147966186807174</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>1.514005598372012E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.7891593638429082</v>
+        <v>0.79175592340149292</v>
       </c>
       <c r="C3">
-        <v>0.04577564021146749</v>
+        <v>3.041845557529366E-2</v>
       </c>
       <c r="D3">
-        <v>0.7765985069782538</v>
+        <v>0.7663745537163259</v>
       </c>
       <c r="E3">
-        <v>0.03999355021936729</v>
+        <v>2.7800888899878771E-2</v>
       </c>
       <c r="F3">
-        <v>0.7561181434599156</v>
+        <v>0.80691333982473223</v>
       </c>
       <c r="G3">
-        <v>0.05711029304873803</v>
+        <v>5.3697250319794242E-2</v>
       </c>
       <c r="H3">
-        <v>0.7714053878610839</v>
+        <v>0.79172346640701063</v>
       </c>
       <c r="I3">
-        <v>0.03745331840421523</v>
+        <v>4.2802273064623808E-2</v>
       </c>
       <c r="J3">
-        <v>0.7766309639727361</v>
+        <v>0.78419344368711452</v>
       </c>
       <c r="K3">
-        <v>0.01171693005374198</v>
+        <v>4.1513307994216563E-2</v>
       </c>
       <c r="L3">
-        <v>0.7690035702693929</v>
+        <v>0.78419344368711452</v>
       </c>
       <c r="M3">
-        <v>0.01702662500299224</v>
+        <v>4.1513307994216563E-2</v>
       </c>
       <c r="N3">
-        <v>0.7842908146705614</v>
+        <v>0.77900032456994484</v>
       </c>
       <c r="O3">
-        <v>0.02336069489424387</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>5.3917261860538947E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.7442680021393495</v>
+        <v>0.75368891914231528</v>
       </c>
       <c r="C4">
-        <v>0.009872846787728927</v>
+        <v>1.3592114327813E-2</v>
       </c>
       <c r="D4">
-        <v>0.7608239736795191</v>
+        <v>0.77075120338406189</v>
       </c>
       <c r="E4">
-        <v>0.004792881513345002</v>
+        <v>2.1782678040778911E-2</v>
       </c>
       <c r="F4">
-        <v>0.7182924101716341</v>
+        <v>0.68083953258456087</v>
       </c>
       <c r="G4">
-        <v>0.06197438983402139</v>
+        <v>3.6368533519209469E-2</v>
       </c>
       <c r="H4">
-        <v>0.7598016239607138</v>
+        <v>0.75979708594674311</v>
       </c>
       <c r="I4">
-        <v>0.01667894113823688</v>
+        <v>2.3043569426904949E-2</v>
       </c>
       <c r="J4">
-        <v>0.7585313041928007</v>
+        <v>0.76260190272442918</v>
       </c>
       <c r="K4">
-        <v>0.01912323950791076</v>
+        <v>1.8121885285846701E-2</v>
       </c>
       <c r="L4">
-        <v>0.7692283755530706</v>
+        <v>0.75852514545955496</v>
       </c>
       <c r="M4">
-        <v>0.01578316434621434</v>
+        <v>1.9890610528630739E-2</v>
       </c>
       <c r="N4">
-        <v>0.7620913761527366</v>
+        <v>0.76285376249979731</v>
       </c>
       <c r="O4">
-        <v>0.02417320668663698</v>
+        <v>2.4288902850876572E-2</v>
       </c>
     </row>
   </sheetData>
@@ -813,11 +828,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -861,145 +876,145 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.8437387096794726</v>
+        <v>0.84962752930510044</v>
       </c>
       <c r="C2">
-        <v>0.01256900327228387</v>
+        <v>1.325641427377439E-2</v>
       </c>
       <c r="D2">
-        <v>0.8430785513711279</v>
+        <v>0.84503521687267558</v>
       </c>
       <c r="E2">
-        <v>0.007775781461952529</v>
+        <v>1.4209564417380209E-2</v>
       </c>
       <c r="F2">
-        <v>0.8199986070546444</v>
+        <v>0.84698347762179904</v>
       </c>
       <c r="G2">
-        <v>0.02270744622635501</v>
+        <v>1.6528189783987939E-2</v>
       </c>
       <c r="H2">
-        <v>0.8415305285884122</v>
+        <v>0.84945980114095376</v>
       </c>
       <c r="I2">
-        <v>0.01115519043987993</v>
+        <v>1.5443174591643009E-2</v>
       </c>
       <c r="J2">
-        <v>0.8489145338124624</v>
+        <v>0.84769228478340641</v>
       </c>
       <c r="K2">
-        <v>0.01111863380652904</v>
+        <v>1.53751521932838E-2</v>
       </c>
       <c r="L2">
-        <v>0.8465922041109341</v>
+        <v>0.84778688378981459</v>
       </c>
       <c r="M2">
-        <v>0.01023912918420117</v>
+        <v>1.516005070158696E-2</v>
       </c>
       <c r="N2">
-        <v>0.843948495719226</v>
+        <v>0.8503131629427656</v>
       </c>
       <c r="O2">
-        <v>0.01514005598372012</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>1.8177221901427981E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.7917559234014929</v>
+        <v>0.77919506653683879</v>
       </c>
       <c r="C3">
-        <v>0.03041845557529366</v>
+        <v>1.4242112905950909E-2</v>
       </c>
       <c r="D3">
-        <v>0.7663745537163259</v>
+        <v>0.78432327166504379</v>
       </c>
       <c r="E3">
-        <v>0.02780088889987877</v>
+        <v>2.3047323035140441E-2</v>
       </c>
       <c r="F3">
-        <v>0.8069133398247322</v>
+        <v>0.78688737422914645</v>
       </c>
       <c r="G3">
-        <v>0.05369725031979424</v>
+        <v>3.2160770923385457E-2</v>
       </c>
       <c r="H3">
-        <v>0.7917234664070106</v>
+        <v>0.77919506653683868</v>
       </c>
       <c r="I3">
-        <v>0.04280227306462381</v>
+        <v>2.7634133655977309E-2</v>
       </c>
       <c r="J3">
-        <v>0.7841934436871145</v>
+        <v>0.78422590068159692</v>
       </c>
       <c r="K3">
-        <v>0.04151330799421656</v>
+        <v>2.4103989790482269E-2</v>
       </c>
       <c r="L3">
-        <v>0.7841934436871145</v>
+        <v>0.78422590068159692</v>
       </c>
       <c r="M3">
-        <v>0.04151330799421656</v>
+        <v>2.4103989790482269E-2</v>
       </c>
       <c r="N3">
-        <v>0.7790003245699448</v>
+        <v>0.79448231093800714</v>
       </c>
       <c r="O3">
-        <v>0.05391726186053895</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2.3711828235776999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.7536889191423153</v>
+        <v>0.77304841088475063</v>
       </c>
       <c r="C4">
-        <v>0.013592114327813</v>
+        <v>2.3616690502615448E-2</v>
       </c>
       <c r="D4">
-        <v>0.7707512033840619</v>
+        <v>0.77356477204583407</v>
       </c>
       <c r="E4">
-        <v>0.02178267804077891</v>
+        <v>2.19440250663419E-2</v>
       </c>
       <c r="F4">
-        <v>0.6808395325845609</v>
+        <v>0.76591173562827186</v>
       </c>
       <c r="G4">
-        <v>0.03636853351920947</v>
+        <v>2.8317261590064521E-2</v>
       </c>
       <c r="H4">
-        <v>0.7597970859467431</v>
+        <v>0.7674436394872044</v>
       </c>
       <c r="I4">
-        <v>0.02304356942690495</v>
+        <v>2.000738032754627E-2</v>
       </c>
       <c r="J4">
-        <v>0.7626019027244292</v>
+        <v>0.77559585744153259</v>
       </c>
       <c r="K4">
-        <v>0.0181218852858467</v>
+        <v>1.9238852095586349E-2</v>
       </c>
       <c r="L4">
-        <v>0.758525145459555</v>
+        <v>0.77483185037519653</v>
       </c>
       <c r="M4">
-        <v>0.01989061052863074</v>
+        <v>1.8745940183896689E-2</v>
       </c>
       <c r="N4">
-        <v>0.7628537624997973</v>
+        <v>0.77024456653862994</v>
       </c>
       <c r="O4">
-        <v>0.02428890285087657</v>
+        <v>2.4100524656907249E-2</v>
       </c>
     </row>
   </sheetData>
